--- a/Team-Data/2012-13/3-13-2012-13.xlsx
+++ b/Team-Data/2012-13/3-13-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,19 +728,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.547</v>
+        <v>0.54</v>
       </c>
       <c r="H2" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I2" t="n">
         <v>37.4</v>
@@ -697,7 +764,7 @@
         <v>13.5</v>
       </c>
       <c r="P2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0.705</v>
@@ -706,10 +773,10 @@
         <v>9.4</v>
       </c>
       <c r="S2" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
         <v>24.4</v>
@@ -718,7 +785,7 @@
         <v>15.1</v>
       </c>
       <c r="W2" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.8</v>
@@ -739,19 +806,19 @@
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF2" t="n">
         <v>11</v>
       </c>
-      <c r="AF2" t="n">
-        <v>10</v>
-      </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -787,25 +854,25 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -814,7 +881,7 @@
         <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.547</v>
+        <v>0.54</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
@@ -861,10 +928,10 @@
         <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L3" t="n">
         <v>5.9</v>
@@ -873,16 +940,16 @@
         <v>16.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R3" t="n">
         <v>8.300000000000001</v>
@@ -894,7 +961,7 @@
         <v>40</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V3" t="n">
         <v>14.5</v>
@@ -909,28 +976,28 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF3" t="n">
         <v>11</v>
       </c>
-      <c r="AF3" t="n">
-        <v>10</v>
-      </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -951,16 +1018,16 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
         <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -969,10 +1036,10 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>11</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1115,13 +1182,13 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>12</v>
@@ -1151,7 +1218,7 @@
         <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
@@ -1160,10 +1227,10 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1178,7 +1245,7 @@
         <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-10</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
         <v>4</v>
@@ -1327,7 +1394,7 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
         <v>28</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
         <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>0.547</v>
+        <v>0.556</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1407,28 +1474,28 @@
         <v>35.3</v>
       </c>
       <c r="J6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.336</v>
+        <v>0.342</v>
       </c>
       <c r="O6" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R6" t="n">
         <v>12.9</v>
@@ -1437,7 +1504,7 @@
         <v>30.6</v>
       </c>
       <c r="T6" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U6" t="n">
         <v>22.8</v>
@@ -1446,10 +1513,10 @@
         <v>14.7</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
         <v>5.9</v>
@@ -1458,16 +1525,16 @@
         <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1476,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1485,10 +1552,10 @@
         <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1497,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO6" t="n">
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ6" t="n">
         <v>5</v>
@@ -1515,7 +1582,7 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>10</v>
@@ -1524,16 +1591,16 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
         <v>16</v>
@@ -1542,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
         <v>23</v>
@@ -1676,7 +1743,7 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN7" t="n">
         <v>20</v>
@@ -1685,10 +1752,10 @@
         <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
         <v>8</v>
@@ -1697,16 +1764,16 @@
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV7" t="n">
         <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1718,7 +1785,7 @@
         <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1846,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
         <v>3</v>
@@ -1855,7 +1922,7 @@
         <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1867,10 +1934,10 @@
         <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR8" t="n">
         <v>26</v>
@@ -1882,16 +1949,16 @@
         <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>5</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1959,34 +2026,34 @@
         <v>0.479</v>
       </c>
       <c r="L9" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
         <v>18.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O9" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="S9" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T9" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U9" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="V9" t="n">
         <v>15.2</v>
@@ -1998,7 +2065,7 @@
         <v>6.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Z9" t="n">
         <v>20.7</v>
@@ -2007,10 +2074,10 @@
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
         <v>2</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2037,13 +2104,13 @@
         <v>4</v>
       </c>
       <c r="AL9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM9" t="n">
         <v>19</v>
       </c>
-      <c r="AM9" t="n">
-        <v>18</v>
-      </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2055,19 +2122,19 @@
         <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2079,10 +2146,10 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.343</v>
+        <v>0.348</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K10" t="n">
         <v>0.444</v>
@@ -2147,28 +2214,28 @@
         <v>17.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O10" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.694</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R10" t="n">
         <v>12.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T10" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2177,7 +2244,7 @@
         <v>6.8</v>
       </c>
       <c r="X10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y10" t="n">
         <v>5.7</v>
@@ -2186,10 +2253,10 @@
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC10" t="n">
         <v>-4</v>
@@ -2201,10 +2268,10 @@
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -2213,10 +2280,10 @@
         <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
@@ -2228,10 +2295,10 @@
         <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>28</v>
@@ -2240,7 +2307,7 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2249,7 +2316,7 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
@@ -2264,7 +2331,7 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
         <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,40 +2384,40 @@
         <v>37.7</v>
       </c>
       <c r="J11" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.398</v>
+        <v>0.397</v>
       </c>
       <c r="O11" t="n">
         <v>17.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.791</v>
+        <v>0.794</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="T11" t="n">
         <v>45</v>
       </c>
       <c r="U11" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V11" t="n">
         <v>15.3</v>
@@ -2359,22 +2426,22 @@
         <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB11" t="n">
         <v>100.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD11" t="n">
         <v>2</v>
@@ -2383,16 +2450,16 @@
         <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2404,19 +2471,19 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
         <v>19</v>
@@ -2425,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
         <v>28</v>
@@ -2440,7 +2507,7 @@
         <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ11" t="n">
         <v>29</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
         <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>0.538</v>
+        <v>0.531</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2499,22 +2566,22 @@
         <v>38.5</v>
       </c>
       <c r="J12" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L12" t="n">
         <v>10.8</v>
       </c>
       <c r="M12" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O12" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
         <v>25.3</v>
@@ -2529,40 +2596,40 @@
         <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U12" t="n">
         <v>23.5</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
         <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA12" t="n">
         <v>20.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.9</v>
+        <v>106.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2574,7 +2641,7 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
@@ -2592,10 +2659,10 @@
         <v>6</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>17</v>
@@ -2625,16 +2692,16 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -2663,34 +2730,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
         <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>0.625</v>
+        <v>0.619</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J13" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N13" t="n">
         <v>0.356</v>
@@ -2699,13 +2766,13 @@
         <v>17.1</v>
       </c>
       <c r="P13" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R13" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S13" t="n">
         <v>32.9</v>
@@ -2723,34 +2790,34 @@
         <v>7.1</v>
       </c>
       <c r="X13" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Y13" t="n">
         <v>5.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA13" t="n">
         <v>21.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.2</v>
+        <v>94</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
       </c>
       <c r="AF13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2771,13 +2838,13 @@
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>14</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>19</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2807,10 +2874,10 @@
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -2845,64 +2912,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="n">
         <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L14" t="n">
         <v>7.5</v>
       </c>
       <c r="M14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.357</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
         <v>16.5</v>
       </c>
       <c r="P14" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T14" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="X14" t="n">
         <v>5.8</v>
@@ -2917,10 +2984,10 @@
         <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="AD14" t="n">
         <v>2</v>
@@ -2938,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ14" t="n">
         <v>24</v>
@@ -2947,13 +3014,13 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
         <v>19</v>
@@ -2965,10 +3032,10 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
         <v>18</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.515</v>
+        <v>0.523</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
@@ -3045,25 +3112,25 @@
         <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>81.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0.6889999999999999</v>
@@ -3078,37 +3145,37 @@
         <v>44.6</v>
       </c>
       <c r="U15" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
         <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.4</v>
+        <v>102.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
         <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AF15" t="n">
         <v>16</v>
@@ -3123,7 +3190,7 @@
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
         <v>8</v>
@@ -3135,10 +3202,10 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3150,28 +3217,28 @@
         <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.698</v>
+        <v>0.694</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,10 +3294,10 @@
         <v>36.5</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
@@ -3239,7 +3306,7 @@
         <v>13.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
         <v>16.2</v>
@@ -3254,10 +3321,10 @@
         <v>13.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U16" t="n">
         <v>21.5</v>
@@ -3266,7 +3333,7 @@
         <v>14.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X16" t="n">
         <v>5.3</v>
@@ -3284,10 +3351,10 @@
         <v>93.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3305,7 +3372,7 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
         <v>16</v>
@@ -3317,25 +3384,25 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>22</v>
@@ -3356,7 +3423,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.778</v>
+        <v>0.774</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J17" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0.495</v>
@@ -3421,22 +3488,22 @@
         <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>0.384</v>
+        <v>0.387</v>
       </c>
       <c r="O17" t="n">
         <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R17" t="n">
         <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T17" t="n">
         <v>38.6</v>
@@ -3448,7 +3515,7 @@
         <v>13.5</v>
       </c>
       <c r="W17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X17" t="n">
         <v>5.1</v>
@@ -3457,22 +3524,22 @@
         <v>3.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AA17" t="n">
         <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.3</v>
+        <v>103.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>1</v>
@@ -3496,7 +3563,7 @@
         <v>7</v>
       </c>
       <c r="AM17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN17" t="n">
         <v>3</v>
@@ -3505,7 +3572,7 @@
         <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -3573,31 +3640,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
         <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.508</v>
+        <v>0.516</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J18" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.439</v>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M18" t="n">
         <v>18.9</v>
@@ -3606,10 +3673,10 @@
         <v>0.357</v>
       </c>
       <c r="O18" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q18" t="n">
         <v>0.737</v>
@@ -3621,7 +3688,7 @@
         <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U18" t="n">
         <v>22.9</v>
@@ -3630,34 +3697,34 @@
         <v>14.3</v>
       </c>
       <c r="W18" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X18" t="n">
         <v>7.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z18" t="n">
         <v>19.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -3678,19 +3745,19 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3708,7 +3775,7 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3720,13 +3787,13 @@
         <v>11</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
       </c>
       <c r="BC18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3779,7 +3846,7 @@
         <v>0.433</v>
       </c>
       <c r="L19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M19" t="n">
         <v>17.9</v>
@@ -3791,25 +3858,25 @@
         <v>18.4</v>
       </c>
       <c r="P19" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R19" t="n">
         <v>12.5</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T19" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U19" t="n">
         <v>22</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
         <v>8.199999999999999</v>
@@ -3821,22 +3888,22 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.3</v>
+        <v>-3</v>
       </c>
       <c r="AD19" t="n">
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
         <v>20</v>
@@ -3851,10 +3918,10 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3866,31 +3933,31 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV19" t="n">
         <v>23</v>
       </c>
       <c r="AW19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>-3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
         <v>26</v>
@@ -4030,7 +4097,7 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ20" t="n">
         <v>25</v>
@@ -4057,13 +4124,13 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
         <v>23</v>
@@ -4081,13 +4148,13 @@
         <v>24</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
         <v>38</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>0.613</v>
+        <v>0.623</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,7 +4204,7 @@
         <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.44</v>
@@ -4149,7 +4216,7 @@
         <v>29.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O21" t="n">
         <v>16.6</v>
@@ -4158,22 +4225,22 @@
         <v>21.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R21" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T21" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U21" t="n">
         <v>19.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W21" t="n">
         <v>8.199999999999999</v>
@@ -4185,16 +4252,16 @@
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA21" t="n">
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
         <v>29</v>
@@ -4206,7 +4273,7 @@
         <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH21" t="n">
         <v>29</v>
@@ -4236,16 +4303,16 @@
         <v>17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
       </c>
       <c r="AS21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT21" t="n">
         <v>21</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>22</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,16 +4330,16 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
       </c>
       <c r="BB21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
         <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.738</v>
+        <v>0.734</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,10 +4386,10 @@
         <v>38.2</v>
       </c>
       <c r="J22" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.483</v>
+        <v>0.482</v>
       </c>
       <c r="L22" t="n">
         <v>7.6</v>
@@ -4334,28 +4401,28 @@
         <v>0.39</v>
       </c>
       <c r="O22" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="P22" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.833</v>
+        <v>0.832</v>
       </c>
       <c r="R22" t="n">
         <v>10.3</v>
       </c>
       <c r="S22" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T22" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W22" t="n">
         <v>8.4</v>
@@ -4367,19 +4434,19 @@
         <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
         <v>106.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,13 +4458,13 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4406,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN22" t="n">
         <v>2</v>
@@ -4433,7 +4500,7 @@
         <v>19</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
         <v>10</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,10 +4640,10 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
         <v>8</v>
@@ -4621,13 +4688,13 @@
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4732,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
         <v>24</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>0.375</v>
+        <v>0.381</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J24" t="n">
         <v>83.90000000000001</v>
@@ -4689,34 +4756,34 @@
         <v>0.442</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M24" t="n">
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.717</v>
+        <v>0.718</v>
       </c>
       <c r="R24" t="n">
         <v>10.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
@@ -4734,7 +4801,7 @@
         <v>18.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
         <v>92.40000000000001</v>
@@ -4743,7 +4810,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -4758,13 +4825,13 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>23</v>
@@ -4773,7 +4840,7 @@
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
@@ -4794,16 +4861,16 @@
         <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
         <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
@@ -4868,43 +4935,43 @@
         <v>84</v>
       </c>
       <c r="K25" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L25" t="n">
         <v>5.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O25" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="P25" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.741</v>
+        <v>0.742</v>
       </c>
       <c r="R25" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T25" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>22.3</v>
       </c>
       <c r="V25" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W25" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X25" t="n">
         <v>5.4</v>
@@ -4916,37 +4983,37 @@
         <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6</v>
+        <v>-5.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
         <v>24</v>
       </c>
-      <c r="AF25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>26</v>
-      </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ25" t="n">
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
         <v>26</v>
@@ -4967,40 +5034,40 @@
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>24</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,13 +5186,13 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
         <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
@@ -5137,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
         <v>20</v>
@@ -5146,7 +5213,7 @@
         <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
         <v>18</v>
@@ -5155,7 +5222,7 @@
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5170,7 +5237,7 @@
         <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -5211,112 +5278,112 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F27" t="n">
         <v>43</v>
       </c>
       <c r="G27" t="n">
-        <v>0.348</v>
+        <v>0.338</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
         <v>83.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="L27" t="n">
         <v>7.2</v>
       </c>
       <c r="M27" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
         <v>23.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R27" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S27" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T27" t="n">
         <v>40.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA27" t="n">
         <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.3</v>
+        <v>-6.1</v>
       </c>
       <c r="AD27" t="n">
         <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ27" t="n">
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
       </c>
       <c r="AM27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN27" t="n">
         <v>10</v>
@@ -5340,16 +5407,16 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV27" t="n">
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5361,10 +5428,10 @@
         <v>14</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,13 +5550,13 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5531,7 +5598,7 @@
         <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.385</v>
+        <v>0.391</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
@@ -5593,7 +5660,7 @@
         <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.442</v>
@@ -5602,10 +5669,10 @@
         <v>7.4</v>
       </c>
       <c r="M29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O29" t="n">
         <v>17.6</v>
@@ -5614,22 +5681,22 @@
         <v>22.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R29" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V29" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
@@ -5638,7 +5705,7 @@
         <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
         <v>22.9</v>
@@ -5647,13 +5714,13 @@
         <v>20</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5668,7 +5735,7 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
         <v>11</v>
@@ -5680,10 +5747,10 @@
         <v>13</v>
       </c>
       <c r="AM29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="n">
         <v>9</v>
@@ -5695,13 +5762,13 @@
         <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>18</v>
@@ -5713,10 +5780,10 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -5757,43 +5824,43 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
         <v>33</v>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30" t="n">
-        <v>0.508</v>
+        <v>0.516</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J30" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N30" t="n">
         <v>0.359</v>
       </c>
       <c r="O30" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P30" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q30" t="n">
         <v>0.767</v>
@@ -5802,16 +5869,16 @@
         <v>12.5</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U30" t="n">
         <v>22.6</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
         <v>8.199999999999999</v>
@@ -5820,22 +5887,22 @@
         <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5853,7 +5920,7 @@
         <v>16</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
         <v>14</v>
@@ -5868,7 +5935,7 @@
         <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
@@ -5877,22 +5944,22 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW30" t="n">
         <v>13</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>11</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
@@ -5939,52 +6006,52 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
         <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O31" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="P31" t="n">
         <v>20.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.735</v>
+        <v>0.739</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S31" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T31" t="n">
         <v>43.5</v>
@@ -5993,7 +6060,7 @@
         <v>21.8</v>
       </c>
       <c r="V31" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
@@ -6011,13 +6078,13 @@
         <v>18.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.1</v>
+        <v>-3.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6035,19 +6102,19 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6056,34 +6123,34 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW31" t="n">
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>25</v>
@@ -6092,7 +6159,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-13-2012-13</t>
+          <t>2013-03-13</t>
         </is>
       </c>
     </row>
